--- a/doanmon/FILE_LOI_3_TRUNG_LAP_VA_CATEGORY.xlsx
+++ b/doanmon/FILE_LOI_3_TRUNG_LAP_VA_CATEGORY.xlsx
@@ -35,10 +35,10 @@
     <t>CAKE-001</t>
   </si>
   <si>
-    <t>First Chocolate Cake</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
+    <t>First Birthday Cake</t>
+  </si>
+  <si>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>This is fine</t>
@@ -47,13 +47,13 @@
     <t>CAKE-002</t>
   </si>
   <si>
-    <t>Vanilla Cake</t>
-  </si>
-  <si>
-    <t>Vanilla</t>
-  </si>
-  <si>
-    <t>Duplicate Chocolate Cake</t>
+    <t>Wedding Cake</t>
+  </si>
+  <si>
+    <t>Wedding Cakes</t>
+  </si>
+  <si>
+    <t>Duplicate Birthday Cake</t>
   </si>
   <si>
     <t>Duplicate productCode CAKE-001</t>
@@ -157,7 +157,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.4609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.69921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.46875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="14.92578125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="8.44140625" customWidth="true" bestFit="true"/>
@@ -192,7 +192,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.99</v>
+        <v>35.99</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>8</v>
@@ -212,7 +212,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>18.5</v>
+        <v>150.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>12</v>
@@ -232,7 +232,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>29.99</v>
+        <v>38.99</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>8</v>
